--- a/artfynd/A 951-2024 artfynd.xlsx
+++ b/artfynd/A 951-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 951-2024 artfynd.xlsx
+++ b/artfynd/A 951-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4250</v>
+        <v>78843929</v>
       </c>
       <c r="B2" t="n">
-        <v>57502</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205995</v>
+        <v>102018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Scheven, 1777)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,19 +708,40 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Eljaröd Vantarödsvägen, Sk</t>
+          <t>Bjärnaboda, Eljaröd, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442163.0984138217</v>
+        <v>442189</v>
       </c>
       <c r="R2" t="n">
-        <v>6172161.76680509</v>
+        <v>6172168</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,55 +760,157 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Vitaby</t>
+          <t>Ravlunda</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-03-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2019-07-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-03-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>artbest ej säker. Mkt liten F-mus flygande dagtid, dags dato dagtid - intressant</t>
+          <t>2019-07-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Mikael Olofsson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Mikael Olofsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>4250</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Eljaröd Vantarödsvägen, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>442163</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6172162</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Simrishamn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vitaby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2009-03-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2009-03-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>artbest ej säker. Mkt liten F-mus flygande dagtid, dags dato dagtid - intressant</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Stefan Lithner</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Stefan Lithner</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
